--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
@@ -15788,7 +15788,7 @@
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>&lt; 10 and &gt; 10^3</t>
+          <t>&lt;10¹ and &gt;10³</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
@@ -15848,12 +15848,12 @@
       </c>
       <c r="V137" s="5" t="inlineStr">
         <is>
-          <t>Microbiology report (Dec 2025)</t>
+          <t>1227/2193/25</t>
         </is>
       </c>
       <c r="W137" s="5" t="inlineStr">
         <is>
-          <t>Issued Dec 2025</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="X137" s="9" t="inlineStr">

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,7 +161,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4768,7 +4767,11 @@
           <t>23.04.2025</t>
         </is>
       </c>
-      <c r="X39" s="18" t="n"/>
+      <c r="X39" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4816,7 +4819,7 @@
           <t>7·10^2</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -5158,7 +5161,7 @@
           <t>7·10^2</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="J43" s="18" t="inlineStr">
         <is>
           <t>&lt;10²&gt;10³</t>
         </is>
@@ -6159,7 +6162,7 @@
           <t>22.43</t>
         </is>
       </c>
-      <c r="E52" s="19" t="inlineStr">
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>24.70</t>
         </is>
@@ -6649,7 +6652,7 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="O56" s="20" t="inlineStr">
+      <c r="O56" s="19" t="inlineStr">
         <is>
           <t>2.06 — DETECTED, &gt;LOQ</t>
         </is>
@@ -9111,7 +9114,7 @@
           <t>2.1×10⁴</t>
         </is>
       </c>
-      <c r="I78" s="19" t="inlineStr">
+      <c r="I78" s="18" t="inlineStr">
         <is>
           <t>3.6×10³</t>
         </is>
@@ -9673,7 +9676,7 @@
           <t>2.8×10⁴</t>
         </is>
       </c>
-      <c r="I83" s="19" t="inlineStr">
+      <c r="I83" s="18" t="inlineStr">
         <is>
           <t>1.7×10⁴</t>
         </is>
@@ -24199,7 +24202,7 @@
           <t>/</t>
         </is>
       </c>
-      <c r="G211" s="19" t="inlineStr">
+      <c r="G211" s="18" t="inlineStr">
         <is>
           <t>"10.3"</t>
         </is>
@@ -24639,7 +24642,7 @@
           <t>/</t>
         </is>
       </c>
-      <c r="G215" s="19" t="inlineStr">
+      <c r="G215" s="18" t="inlineStr">
         <is>
           <t>"10.3"</t>
         </is>
@@ -27697,49 +27700,49 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="21" t="inlineStr">
+      <c r="A242" s="20" t="inlineStr">
         <is>
           <t>*BLQ — под лимит на квантификација (below limit of quantification)</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="21" t="inlineStr">
+      <c r="A243" s="20" t="inlineStr">
         <is>
           <t>*LOQ — лимит на квантификација (limit of quantification)</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="21" t="inlineStr">
+      <c r="A244" s="20" t="inlineStr">
         <is>
           <t>*n.d — not detected</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="21" t="inlineStr">
+      <c r="A245" s="20" t="inlineStr">
         <is>
           <t>*"/" — параметарот не е опфатен со тој извештај (not covered by that report)</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="21" t="inlineStr">
+      <c r="A246" s="20" t="inlineStr">
         <is>
           <t>*"not tested" — микотоксинскиот под-параметар не е анализиран на сертификат со само вкупни афлатоксини</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="22" t="inlineStr">
+      <c r="A247" s="21" t="inlineStr">
         <is>
           <t>*црвена боја — означува отстапка од спецификација (deviation from specification)</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="23" t="inlineStr">
+      <c r="A248" s="22" t="inlineStr">
         <is>
           <t>*портокалова боја — лабораториски наод или забелешка за интегритет на податоци</t>
         </is>
@@ -27792,207 +27795,208 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X50" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X51" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X52" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X53" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X54" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X55" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X56" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X57" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X58" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X59" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X60" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X61" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X62" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X63" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X65" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X66" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X68" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X69" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X70" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X71" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X72" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X73" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X74" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X75" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X76" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X77" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X78" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X79" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X80" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X81" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X84" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X85" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X86" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X87" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X88" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X89" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X90" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X91" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X92" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X95" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X96" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X97" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X98" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X99" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X100" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X101" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X102" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X103" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X104" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X105" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X106" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X107" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X108" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X109" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X110" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X111" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X112" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X113" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X114" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X115" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X116" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X117" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X118" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X119" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X120" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X121" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X122" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X123" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X124" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X125" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X126" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X127" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X128" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X129" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X130" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X131" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X132" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X133" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X134" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X135" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X136" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X137" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X138" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X139" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X140" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X141" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X142" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X143" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X144" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X145" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X146" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X147" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X148" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X149" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X150" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X151" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X152" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X153" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X154" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X155" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X156" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X157" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X158" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X159" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X160" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X161" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X162" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X163" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X164" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X165" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X166" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X167" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X168" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X169" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X170" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X171" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X172" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X173" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X174" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X175" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X176" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X177" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X178" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X179" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X180" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X181" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X182" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X183" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X184" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X185" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X186" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X187" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X188" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X189" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X190" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X191" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X192" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X193" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X194" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X195" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X196" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X197" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X198" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X199" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X200" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X201" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X202" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X203" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X204" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X205" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X206" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X207" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X208" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X209" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X210" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X211" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X212" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X213" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X214" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X215" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X216" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X217" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X218" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X219" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X220" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X221" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X222" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X223" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X224" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X225" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X226" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X227" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X228" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X229" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X230" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X231" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X232" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X233" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X234" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X235" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X236" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X237" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X238" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X239" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X240" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X157" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X158" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X159" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X160" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X161" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X165" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X166" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X167" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X168" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X169" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X170" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X171" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X172" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X173" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X174" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X175" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X176" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X177" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X178" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X179" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X180" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X181" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X182" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X183" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X184" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X185" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X186" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X187" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X188" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X189" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X190" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X191" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X192" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X193" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X194" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X195" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X196" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X197" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X198" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X199" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X200" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X201" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X202" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X203" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X204" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X205" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X206" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X207" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X208" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X209" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X210" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X211" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X212" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X213" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X214" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X215" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X216" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X217" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X218" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X219" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X220" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X221" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X222" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X223" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X224" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X225" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X226" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X227" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X228" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X229" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X230" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X231" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X232" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X233" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X234" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X235" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X236" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X237" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X238" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X239" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X240" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Production_Batches_QC_Result_Table.xlsx
@@ -13606,7 +13606,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="C199" s="15" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr">
